--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACC 63/LTAIPT_A63BIS.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACC 63/LTAIPT_A63BIS.xlsx
@@ -10,17 +10,21 @@
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
+    <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
+    <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$11</definedName>
-    <definedName name="Hidden_212">Hidden_2!$A$1:$A$3</definedName>
+    <definedName name="Hidden_25">Hidden_2!$A$1:$A$11</definedName>
+    <definedName name="Hidden_313">Hidden_3!$A$1:$A$2</definedName>
+    <definedName name="Hidden_414">Hidden_4!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="190">
   <si>
     <t>48959</t>
   </si>
@@ -73,6 +77,9 @@
     <t>435897</t>
   </si>
   <si>
+    <t>571920</t>
+  </si>
+  <si>
     <t>435905</t>
   </si>
   <si>
@@ -94,6 +101,9 @@
     <t>435892</t>
   </si>
   <si>
+    <t>571921</t>
+  </si>
+  <si>
     <t>435896</t>
   </si>
   <si>
@@ -124,13 +134,16 @@
     <t>Fecha de término del periodo que se informa</t>
   </si>
   <si>
-    <t>Tipo de integrante del sujeto obligado (catálogo)</t>
+    <t>ESTE CRITERIO APLICA PARA EJERCICIOS ANTERIORES AL 01/04/2023 -&gt; Tipo de integrante del sujeto obligado (catálogo)</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Tipo de integrante del sujeto obligado (catálogo)</t>
   </si>
   <si>
     <t>Clave o nivel del puesto</t>
   </si>
   <si>
-    <t xml:space="preserve">Denominación del puesto </t>
+    <t>Denominación del puesto (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Denominación del cargo</t>
@@ -148,6 +161,9 @@
     <t>Segundo apellido del(la) servidor(a) público(a)</t>
   </si>
   <si>
+    <t xml:space="preserve">ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)	</t>
+  </si>
+  <si>
     <t>Modalidad de la Declaración Patrimonial (catálogo)</t>
   </si>
   <si>
@@ -166,43 +182,370 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>B9FE5E1F562CB1B7A173C1ECB3341DF5</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>DD28A230DF7B759A8775A9B20AF5DB47</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>Servidor(a) público(a)</t>
+  </si>
+  <si>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
+    <t>EH8619</t>
+  </si>
+  <si>
+    <t>Docente</t>
+  </si>
+  <si>
+    <t>Docente CBI</t>
+  </si>
+  <si>
+    <t>Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>Romano</t>
+  </si>
+  <si>
+    <t>Cortes</t>
+  </si>
+  <si>
+    <t>Inicio</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_INICIO_OSCAR-ROMANO-CORTES.pdf</t>
+  </si>
+  <si>
+    <t>Contraloria Interna</t>
+  </si>
+  <si>
+    <t>24/04/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Ver nota</t>
-  </si>
-  <si>
-    <t>16/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo  del 01 de octubre de 2022 al 31 de diciembre de 2022,  el personal adscrito del Colegio de Bachilleres del Estado de Tlaxcala no cuenta con información de las Declaraciones Patrimoniales ya que la fecha límite  para presentarla  de  acuerdo a lo establecido en los artículos 46 y 47 de la Ley General de Responsabilidades Administrativas solo se presenta hasta  el 31 de de mayo del ejercicio 2022.</t>
-  </si>
-  <si>
-    <t>Servidor(a) público(a)</t>
-  </si>
-  <si>
-    <t>Inicio</t>
+    <t>DEE66D0A734481A9B23F014FCCF8DFA5</t>
   </si>
   <si>
     <t>Funcionario</t>
   </si>
   <si>
+    <t>No Aplica</t>
+  </si>
+  <si>
+    <t>Inventarios</t>
+  </si>
+  <si>
+    <t>Departamento de Inventarios</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>Martínez</t>
+  </si>
+  <si>
+    <t>Herman</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_INICIO_JORGE-MARTINEZ-HERMAN.pdf</t>
+  </si>
+  <si>
+    <t>5FC293EBDBE53F35556F94B214ABC244</t>
+  </si>
+  <si>
+    <t>Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Arianna</t>
+  </si>
+  <si>
+    <t>Tecpa</t>
+  </si>
+  <si>
+    <t>Sartillo</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_INICIO_ARIANNA-TECPA-SARTILLO.pdf</t>
+  </si>
+  <si>
+    <t>DC2CD8F2F26E20361E39620220DE4957</t>
+  </si>
+  <si>
+    <t>Director De Área</t>
+  </si>
+  <si>
+    <t>Direccion Académica</t>
+  </si>
+  <si>
+    <t>Norberto</t>
+  </si>
+  <si>
+    <t>Cervantes</t>
+  </si>
+  <si>
+    <t>Contreras</t>
+  </si>
+  <si>
+    <t>Conclusión</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_CONCLUSION_NORBERTO-CERVANTES-CONTRERAS.pdf</t>
+  </si>
+  <si>
+    <t>525A208155FCCA5011F9821194703238</t>
+  </si>
+  <si>
+    <t>A08004</t>
+  </si>
+  <si>
+    <t>Taquimecanógrafa</t>
+  </si>
+  <si>
+    <t>Taquimecanografa</t>
+  </si>
+  <si>
+    <t>Recurso Humanos</t>
+  </si>
+  <si>
+    <t>Maricela</t>
+  </si>
+  <si>
+    <t>Pérez</t>
+  </si>
+  <si>
+    <t>Sánchez</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_INICIO_MARICELA-PEREZ-SANCHEZ.pdf</t>
+  </si>
+  <si>
+    <t>BF814AA6B1BEABAF394EEDBF1FA86212</t>
+  </si>
+  <si>
+    <t>Plantel 01 Tlaxcala</t>
+  </si>
+  <si>
+    <t>Karina</t>
+  </si>
+  <si>
+    <t>Teomitzi</t>
+  </si>
+  <si>
     <t>Modificación</t>
   </si>
   <si>
-    <t>Conclusión</t>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_MODIFICACION_KARINA-TEOMITZI-TEOMITZI.pdf</t>
+  </si>
+  <si>
+    <t>4B8C5CA4CAB841DA15CE70BF282101D4</t>
+  </si>
+  <si>
+    <t>S06002</t>
+  </si>
+  <si>
+    <t>Intendencia</t>
+  </si>
+  <si>
+    <t>Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Ma. Felicitas Alejandrina</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>Fragoso</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_CONCLUSION_MA.-FELICITAS-ALEJANDRINA-TORRES-FRAGOSO.pdf</t>
+  </si>
+  <si>
+    <t>3004A8FF0F1218994CCE7B378C667CE6</t>
+  </si>
+  <si>
+    <t>CF18092</t>
+  </si>
+  <si>
+    <t>Jefe de Servicios Generales</t>
+  </si>
+  <si>
+    <t>Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Chamorro</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_INICIO_LUIS-PEREZ-CHAMORRO.pdf</t>
+  </si>
+  <si>
+    <t>CA75A062E9920812BF4FED37FB989D44</t>
+  </si>
+  <si>
+    <t>CF12010</t>
+  </si>
+  <si>
+    <t>Capturista</t>
+  </si>
+  <si>
+    <t>Plantel 18 Atltzayanca</t>
+  </si>
+  <si>
+    <t>Ivonne</t>
+  </si>
+  <si>
+    <t>Breton</t>
+  </si>
+  <si>
+    <t>García</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_INICIO_IVONNE-BRETON-GARCIA.pdf</t>
+  </si>
+  <si>
+    <t>58587A88E69474D12883D83FEE6205F9</t>
+  </si>
+  <si>
+    <t>Director del Plante 15 Hueyotlipan</t>
+  </si>
+  <si>
+    <t>Director Del Plante 15 Hueyotlipan</t>
+  </si>
+  <si>
+    <t>Plantel 15 Hueyotlipan</t>
+  </si>
+  <si>
+    <t>Alejandro</t>
+  </si>
+  <si>
+    <t>Zempoalteca</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_INICIO_ALEJANDRO-ZEMPOALTECA-ZEMPOALTECA.pdf</t>
+  </si>
+  <si>
+    <t>D9FB0B0FDFE4008583AD13672121EB65</t>
+  </si>
+  <si>
+    <t>Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>Vianey</t>
+  </si>
+  <si>
+    <t>Peralta</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_INICIO_VIANEY-ALEJANDRO-PERALTA.pdf</t>
+  </si>
+  <si>
+    <t>F58D28AF35190CC3163E96F3639A7609</t>
+  </si>
+  <si>
+    <t>Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>Alejandro Enrique</t>
+  </si>
+  <si>
+    <t>Águila</t>
+  </si>
+  <si>
+    <t>Rivera</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_INICIO_ALEJANDRO-ENRIQUE-AGUILA-RIVERA.pdf</t>
+  </si>
+  <si>
+    <t>F7C38276F1E0CFEB91AD8E17FE621E1C</t>
+  </si>
+  <si>
+    <t>Docente Interino</t>
+  </si>
+  <si>
+    <t>Plantel 08 Ixtacuixtla</t>
+  </si>
+  <si>
+    <t>Sonia</t>
+  </si>
+  <si>
+    <t>López</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202023/043/2023_INICIO_SONIA-LOPEZ-RIVERA.pdf</t>
+  </si>
+  <si>
+    <t>AE1733E459F9E3893ED4B1EEAE84F38F</t>
+  </si>
+  <si>
+    <t>Recursos Humanos</t>
+  </si>
+  <si>
+    <t>Ximena</t>
+  </si>
+  <si>
+    <t>Sandoval</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202023/043/2023_INICIO_XIMENA-RIVERA-SANDOVAL.pdf</t>
+  </si>
+  <si>
+    <t>DFDCE4717A1FA40BDCB60A3D1E0AD83B</t>
+  </si>
+  <si>
+    <t>Jefe de Materia</t>
+  </si>
+  <si>
+    <t>Subdirección Académica</t>
+  </si>
+  <si>
+    <t>Asunción</t>
+  </si>
+  <si>
+    <t>Nava</t>
+  </si>
+  <si>
+    <t>Acoltzi</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202023/043/2022_CONCLUSION_ASUNCION-NAVA-ACOLTZI.pdf</t>
+  </si>
+  <si>
+    <t>CCF95B4D4D597860AEBDA54E6062D611</t>
+  </si>
+  <si>
+    <t>CF33116</t>
+  </si>
+  <si>
+    <t>Técnico Especializado</t>
+  </si>
+  <si>
+    <t>Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>Yazmin</t>
+  </si>
+  <si>
+    <t>Licona</t>
+  </si>
+  <si>
+    <t>https://sfp.tlaxcala.gob.mx/transparencia/juridico/individuales%202022/043/2022_CONCLUSION_YAZMIN-SANCHEZ-LICONA.pdf</t>
   </si>
   <si>
     <t>Servidor[a] público[a] eventual</t>
@@ -230,6 +573,27 @@
   </si>
   <si>
     <t>Otro</t>
+  </si>
+  <si>
+    <t>Funcionario [a]</t>
+  </si>
+  <si>
+    <t>Empleado [a]</t>
+  </si>
+  <si>
+    <t>Integrante del poder judicial</t>
+  </si>
+  <si>
+    <t>Integrante de órgano autónomo</t>
+  </si>
+  <si>
+    <t>Prestador[a] de servicios profesionales</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -622,34 +986,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="52.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="130.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="255" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="102.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="125.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -666,7 +1033,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -681,7 +1048,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -695,7 +1062,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
         <v>6</v>
@@ -716,25 +1083,31 @@
         <v>6</v>
       </c>
       <c r="M4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" t="s">
         <v>8</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" t="s">
         <v>9</v>
       </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
         <v>10</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="S4" t="s">
         <v>11</v>
       </c>
-      <c r="R4" t="s">
+      <c r="T4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -786,10 +1159,16 @@
       <c r="R5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S5" t="s">
+        <v>30</v>
+      </c>
+      <c r="T5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -808,119 +1187,1063 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-    </row>
-    <row r="7" spans="1:18" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+    </row>
+    <row r="7" spans="1:20" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="O8" s="2" t="s">
+      <c r="C12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:R6"/>
+    <mergeCell ref="A6:T6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -928,12 +2251,18 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M8">
-      <formula1>Hidden_212</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F201">
+      <formula1>Hidden_25</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N8:N201">
+      <formula1>Hidden_313</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O8:O201">
+      <formula1>Hidden_414</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -947,7 +2276,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -957,47 +2286,47 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -1007,22 +2336,107 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
